--- a/aq_files/0444.xlsx
+++ b/aq_files/0444.xlsx
@@ -1,189 +1,273 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
-  <si>
-    <t>Decision Tree Modeling</t>
-  </si>
-  <si>
-    <t>Which Python library provides Decision Tree implementation?</t>
-  </si>
-  <si>
-    <t>Which function in scikit-learn is used to create a Decision Tree classifier?</t>
-  </si>
-  <si>
-    <t>How do you split your dataset into training and testing sets?</t>
-  </si>
-  <si>
-    <t>How do you fit a Decision Tree model to training data?</t>
-  </si>
-  <si>
-    <t>How do you make predictions on new data using a trained Decision Tree?</t>
-  </si>
-  <si>
-    <t>How do you visualize a Decision Tree in Python?</t>
-  </si>
-  <si>
-    <t>How do you evaluate Decision Tree accuracy on test data?</t>
-  </si>
-  <si>
-    <t>How do you create a confusion matrix for Decision Tree predictions?</t>
-  </si>
-  <si>
-    <t>How do you calculate precision, recall, and F1-score for a Decision Tree?</t>
-  </si>
-  <si>
-    <t>How do you control overfitting in a Decision Tree using parameters like max_depth or min_samples_leaf?</t>
-  </si>
-  <si>
-    <t>Random Forest Modeling</t>
-  </si>
-  <si>
-    <t>Which function in scikit-learn is used to create a Random Forest classifier?</t>
-  </si>
-  <si>
-    <t>How do you fit a Random Forest model to training data?</t>
-  </si>
-  <si>
-    <t>How do you make predictions using a trained Random Forest?</t>
-  </si>
-  <si>
-    <t>How do you evaluate Random Forest accuracy on test data?</t>
-  </si>
-  <si>
-    <t>How do you compute feature importance in a Random Forest?</t>
-  </si>
-  <si>
-    <t>How do you handle multi-class classification with Random Forest in Python?</t>
-  </si>
-  <si>
-    <t>How do you use cross-validation to evaluate a Random Forest model?</t>
-  </si>
-  <si>
-    <t>How do you tune hyperparameters like n_estimators and max_features for better performance?</t>
-  </si>
-  <si>
-    <t>How do you calculate out-of-bag (OOB) error in Random Forest?</t>
-  </si>
-  <si>
-    <t>How do you save and load trained Decision Tree or Random Forest models in Python?</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="10.0"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Sheets">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="000000"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4285F4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EA4335"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="FBBC04"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="34A853"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="FF6D01"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="46BDC6"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Sheets">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -324,127 +408,698 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>What is a tree map chart best used for?</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Showing trends over time</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Displaying hierarchical data as nested rectangles</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Comparing categories</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Showing distribution of data</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>In a tree map, what does the size of each rectangle represent?</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>The category name</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>The value or proportion of that category</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>The time period</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>The color only</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>In a tree map, what does the color of each rectangle often represent?</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>The category name</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>An additional variable or value (like growth rate)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>The time period</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>The size only</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A tree map is particularly useful for:</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Showing detailed trends over time</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Visualizing hierarchical data and comparing proportions</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Showing exact values</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Showing relationships between variables</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>What does a tree map show that a pie chart does not?</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Proportions</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Hierarchical relationships and nested categories</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Trends</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Exact values</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Which chart best shows the sales of categories and subcategories together?</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Line chart</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Tree map</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Bar chart</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Box plot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>If Electronics has the largest sales, what would its rectangle look like in a tree map?</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>The smallest rectangle</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>The largest rectangle</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>A circle</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>A line</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
-        <v>8</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Within the Electronics rectangle, Laptops, Phones, and Tablets would be shown as:</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Separate charts</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Smaller rectangles inside the Electronics rectangle</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Circles</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Lines</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
-        <v>9</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>If Laptops have the highest sales among Electronics, what would its rectangle look like?</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>The smallest rectangle inside Electronics</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>The largest rectangle inside Electronics</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Outside the Electronics rectangle</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Equal to others</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>10</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>In Excel, where can you find the tree map chart option?</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Insert &gt; Charts &gt; Tree Map</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Insert &gt; Charts &gt; Line</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Insert &gt; Charts &gt; Bar</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Insert &gt; Charts &gt; Pie</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A tree map is especially useful when:</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>You have only one category</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>You have hierarchical data with many categories and subcategories</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>You want to show trends over time</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>You have only a few data points</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
-        <v>12</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>What is the main advantage of a tree map over a pie chart?</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>It shows exact values</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>It can display hierarchical data and multiple categories efficiently</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>It shows trends</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>It is easier to create</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
-        <v>13</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>What does a tree map help answer?</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>What is the trend over time?</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>What is the distribution across categories and subcategories?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>What is the correlation between variables?</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>What is the average value?</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
-        <v>14</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Which chart best shows traffic from each source and sub-source?</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Line chart</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Tree map</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Bar chart</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Box plot</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
-        <v>15</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>If Google has the most traffic among Search, what would its rectangle look like?</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>The smallest</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>The largest</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>A circle</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>A line</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
-        <v>16</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>The tree map allows you to see:</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Only the total traffic</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Both the overall source contributions and sub-source breakdowns</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Only the sub-source breakdowns</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Trends over time</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
-        <v>17</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>If Social has the smallest overall traffic, what would its rectangle look like?</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>The largest rectangle</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>The smallest rectangle</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Equal to others</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Not shown</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
-        <v>18</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Which statement about tree maps is TRUE?</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>They are best for showing trends over time</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>They use nested rectangles to show hierarchical data</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>They cannot show negative values</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>They are the same as pie charts</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
-        <v>19</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A tree map is most similar to which of the following?</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Line chart</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Bar chart</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Hierarchical pie chart with nested slices</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Scatter plot</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="s">
-        <v>21</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>When should you use a tree map instead of a bar chart?</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>When you want to show trends</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>When you have hierarchical data and want to show proportions across multiple levels</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>When you have only two categories</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>When you want to show exact values</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>